--- a/it_forms/004_data_warehouse_assessment_questionnaire--it_forms.xlsx
+++ b/it_forms/004_data_warehouse_assessment_questionnaire--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>performance_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is this data warehouse platform meeting your performance expectations?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>questions_2</t>
+          <t>refresh_frequency_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is the data refresh frequency meeting your expectations?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>questions_3</t>
+          <t>improvement_priorities_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>What are your improvement priorities for the data warehouse platform?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>questions_4</t>
+          <t>performance_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>What are some key performance issues with this platform?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,35 +635,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>questions_5</t>
+          <t>data_quality_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is the data quality of this data warehouse platform meeting your expectations?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>questions_6</t>
+          <t>data_governance_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is the current data governance of your data warehouse platform meeting your expectations?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>questions_7</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is this data warehouse platform the largest for your business?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>questions_8</t>
+          <t>multiple_environments_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Is this data warehouse platform used in multiple environments?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>questions_9</t>
+          <t>refresh_frequency_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>What refresh frequencies would be ideal for your data warehouse platform?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,39 +750,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>questions_10</t>
+          <t>additional_comments_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Do you have any additional comments about this data warehouse platform?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>questions_11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,289 +804,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>questions_choices</t>
+          <t>performance_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>is_this_the_primary_data_warehouse_platform_for_your_business?</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Is this the primary data warehouse platform for your business?</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>questions_choices</t>
+          <t>performance_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>is_this_data_warehouse_platform_the_largest_for_your_business?</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Is this data warehouse platform the largest for your business?</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>questions_choices</t>
+          <t>refresh_frequency_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>does_this_data_warehouse_platform_have_multiple_environments?</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Does this data warehouse platform have multiple environments?</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>questions_2_choices</t>
+          <t>refresh_frequency_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>is_the_data_quality_of_your_data_warehouse_platform_meeting_your_expectations?</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Is the data quality of your data warehouse platform meeting your expectations?</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>questions_2_choices</t>
+          <t>improvement_priorities_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>is_the_refresh_frequency_of_your_data_warehouse_platform_meeting_your_expectations?</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Is the refresh frequency of your data warehouse platform meeting your expectations?</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>questions_3_choices</t>
+          <t>improvement_priorities_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>are_you_happy_with_the_current_performance_of_your_data_warehouse_platform?</t>
+          <t>data_quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Are you happy with the current performance of your data warehouse platform?</t>
+          <t>Data Quality</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>questions_3_choices</t>
+          <t>improvement_priorities_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>are_you_happy_with_the_current_performance_of_your_data_warehouse_platform?</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Are you happy with the current performance of your data warehouse platform?</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>questions_4_choices</t>
+          <t>performance_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>is_the_data_governance_of_your_data_warehouse_platform_meeting_your_expectations?</t>
+          <t>data_refresh_times_are_too_long</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Is the data governance of your data warehouse platform meeting your expectations?</t>
+          <t>Data refresh times are too long</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>questions_4_choices</t>
+          <t>performance_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>is_the_data_governance_of_your_data_warehouse_platform_meeting_your_expectations?</t>
+          <t>data_is_not_up-to-date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Is the data governance of your data warehouse platform meeting your expectations?</t>
+          <t>Data is not up-to-date</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>questions_5_choices</t>
+          <t>performance_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>has_the_performance_of_your_data_warehouse_platform_met_your_expectations?</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Has the performance of your data warehouse platform met your expectations?</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>questions_5_choices</t>
+          <t>data_quality_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>has_the_performance_of_your_data_warehouse_platform_met_your_expectations?</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Has the performance of your data warehouse platform met your expectations?</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>questions_6_choices</t>
+          <t>data_quality_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what_are_your_improvement_priorities_for_the_data_warehouse_platform?</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What are your improvement priorities for the data warehouse platform?</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>questions_6_choices</t>
+          <t>data_governance_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what_are_your_improvement_priorities_for_the_data_warehouse_platform?</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What are your improvement priorities for the data warehouse platform?</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>questions_7_choices</t>
+          <t>data_governance_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>what_refresh_frequencies_would_be_ideal_for_your_data_warehouse_platform?</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What refresh frequencies would be ideal for your data warehouse platform?</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>questions_7_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>questions_8_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>what_refresh_frequencies_would_be_ideal_for_your_data_warehouse_platform?</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What refresh frequencies would be ideal for your data warehouse platform?</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>questions_8_choices</t>
+          <t>multiple_environments_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>multiple_environments_1_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>refresh_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>refresh_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>refresh_frequency_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
